--- a/artfynd/S 2726-2025 artfynd.xlsx
+++ b/artfynd/S 2726-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY59"/>
+  <dimension ref="A1:AZ59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Kartläggning av Ängelholms kommun 2022</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102307243</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>Kartläggning av Ängelholms kommun 2022</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102307268</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
           <t>Kartläggning av Ängelholms kommun 2022</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102317095</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1106,6 +1126,11 @@
           <t>Projekt Skånes mossor</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98165102</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1222,6 +1247,11 @@
           <t>Projekt Skånes mossor</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98165086</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1358,6 +1388,11 @@
           <t>Projekt Skånes mossor</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98165079</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1474,6 +1509,11 @@
           <t>Skånes Flora (1989-2006)</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/64042685</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1590,6 +1630,11 @@
           <t>Skånes Flora (1989-2006)</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/64042688</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1691,6 +1736,11 @@
           <t>Kartläggning av Ängelholms kommun 2022</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103640015</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1792,6 +1842,11 @@
           <t>Kartläggning av Ängelholms kommun 2022</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103640012</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1893,6 +1948,11 @@
           <t>Kartläggning av Ängelholms kommun 2022</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103640014</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2033,6 +2093,11 @@
           <t>Projekt Skånes mossor</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98164996</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2169,6 +2234,11 @@
           <t>Projekt Skånes mossor</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98164967</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2285,6 +2355,11 @@
           <t>Projekt Skånes mossor</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98164974</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2421,6 +2496,11 @@
           <t>Projekt Skånes mossor</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98164943</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2522,6 +2602,11 @@
           <t>Kartläggning av Ängelholms kommun 2022</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102316996</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2623,6 +2708,11 @@
           <t>Kartläggning av Ängelholms kommun 2022</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102317011</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2724,6 +2814,11 @@
           <t>Kartläggning av Ängelholms kommun 2022</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102317022</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2825,6 +2920,11 @@
           <t>Kartläggning av Ängelholms kommun 2022</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102317056</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2926,6 +3026,11 @@
           <t>Kartläggning av Ängelholms kommun 2022</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102317003</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3057,6 +3162,11 @@
           <t>Projekt Skånes mossor</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98165626</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3158,6 +3268,11 @@
           <t>Kartläggning av Ängelholms kommun 2022</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102317030</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3284,6 +3399,11 @@
           <t>Projekt Skånes mossor</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104833549</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3385,6 +3505,11 @@
           <t>Kartläggning av Ängelholms kommun 2022</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102317001</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3486,6 +3611,11 @@
           <t>Kartläggning av Ängelholms kommun 2022</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102317015</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3587,6 +3717,11 @@
           <t>Kartläggning av Ängelholms kommun 2022</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102317018</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3688,6 +3823,11 @@
           <t>Kartläggning av Ängelholms kommun 2022</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102317002</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3789,6 +3929,11 @@
           <t>Kartläggning av Ängelholms kommun 2022</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102317014</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3890,6 +4035,11 @@
           <t>Kartläggning av Ängelholms kommun 2022</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102317019</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3991,6 +4141,11 @@
           <t>Kartläggning av Ängelholms kommun 2022</t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102317051</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4092,6 +4247,11 @@
           <t>Kartläggning av Ängelholms kommun 2022</t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102317057</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4227,6 +4387,11 @@
           <t>Projekt Skånes mossor</t>
         </is>
       </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98165633</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4363,6 +4528,11 @@
           <t>Projekt Skånes mossor</t>
         </is>
       </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98165653</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4464,6 +4634,11 @@
           <t>Kartläggning av Ängelholms kommun 2022</t>
         </is>
       </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102317007</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4565,6 +4740,11 @@
           <t>Kartläggning av Ängelholms kommun 2022</t>
         </is>
       </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102317026</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4666,6 +4846,11 @@
           <t>Kartläggning av Ängelholms kommun 2022</t>
         </is>
       </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102317042</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4792,6 +4977,11 @@
           <t>Projekt Skånes mossor</t>
         </is>
       </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98165652</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4893,6 +5083,11 @@
           <t>Kartläggning av Ängelholms kommun 2022</t>
         </is>
       </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102317006</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4994,6 +5189,11 @@
           <t>Kartläggning av Ängelholms kommun 2022</t>
         </is>
       </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102317025</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5095,6 +5295,11 @@
           <t>Kartläggning av Ängelholms kommun 2022</t>
         </is>
       </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102317041</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5196,6 +5401,11 @@
           <t>Kartläggning av Ängelholms kommun 2022</t>
         </is>
       </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102317067</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5312,6 +5522,11 @@
           <t>Projekt Skånes mossor</t>
         </is>
       </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98165654</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5413,6 +5628,11 @@
           <t>Kartläggning av Ängelholms kommun 2022</t>
         </is>
       </c>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102316998</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5514,6 +5734,11 @@
           <t>Kartläggning av Ängelholms kommun 2022</t>
         </is>
       </c>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102317004</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5615,6 +5840,11 @@
           <t>Kartläggning av Ängelholms kommun 2022</t>
         </is>
       </c>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102317029</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5745,6 +5975,11 @@
           <t>Projekt Skånes mossor</t>
         </is>
       </c>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104833546</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5846,6 +6081,11 @@
           <t>Kartläggning av Ängelholms kommun 2022</t>
         </is>
       </c>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102316997</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5947,6 +6187,11 @@
           <t>Kartläggning av Ängelholms kommun 2022</t>
         </is>
       </c>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102317008</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6048,6 +6293,11 @@
           <t>Kartläggning av Ängelholms kommun 2022</t>
         </is>
       </c>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102317028</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6149,6 +6399,11 @@
           <t>Kartläggning av Ängelholms kommun 2022</t>
         </is>
       </c>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102317034</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6250,6 +6505,11 @@
           <t>Kartläggning av Ängelholms kommun 2022</t>
         </is>
       </c>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102317037</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6351,6 +6611,11 @@
           <t>Kartläggning av Ängelholms kommun 2022</t>
         </is>
       </c>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102317060</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6452,6 +6717,11 @@
           <t>Kartläggning av Ängelholms kommun 2022</t>
         </is>
       </c>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102317016</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6553,6 +6823,11 @@
           <t>Kartläggning av Ängelholms kommun 2022</t>
         </is>
       </c>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102317061</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6654,6 +6929,11 @@
           <t>Kartläggning av Ängelholms kommun 2022</t>
         </is>
       </c>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102317032</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6755,6 +7035,11 @@
           <t>Kartläggning av Ängelholms kommun 2022</t>
         </is>
       </c>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102317045</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6856,6 +7141,11 @@
           <t>Kartläggning av Ängelholms kommun 2022</t>
         </is>
       </c>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102317064</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6958,8 +7248,73 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131074774</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>